--- a/Funding Formula Modeling Workbook.xlsx
+++ b/Funding Formula Modeling Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etsu365-my.sharepoint.com/personal/balioc_etsu_edu/Documents/RHERC 2_2024-2028/RHERC Year 1_Formula Supplement/4. Dissemination/Policy Brief/GitHub Materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D6F874B5-DA98-D746-B160-37BB0D9301AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A308D210-2FE0-004F-8D9C-85A83E2FB6F1}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{D6F874B5-DA98-D746-B160-37BB0D9301AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E455CFE-A7FC-704F-988D-45C8137C1D94}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="17780" windowHeight="17180" xr2:uid="{1821E6E1-57F7-43BF-9025-87F83BF5211A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="20320" windowHeight="17180" xr2:uid="{1821E6E1-57F7-43BF-9025-87F83BF5211A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1. Introduction" sheetId="1" r:id="rId1"/>
@@ -793,73 +793,18 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:colOff>139390</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>130661</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>6869</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>97509</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2625DA2A-1556-476C-8B63-3F8D760FEA8D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="95250" y="123825"/>
-          <a:ext cx="5398019" cy="4130048"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>161636</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>23090</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>115019</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -874,8 +819,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6182264" y="161636"/>
-          <a:ext cx="11151166" cy="4582892"/>
+          <a:off x="139390" y="130661"/>
+          <a:ext cx="9284010" cy="5089039"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -910,17 +855,29 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" u="sng" baseline="0"/>
+            <a:rPr lang="en-US" sz="1600" u="sng" baseline="0"/>
             <a:t>Introduction</a:t>
           </a:r>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" u="none" baseline="0"/>
-            <a:t>This workbook is designed to allow for easy calculation of funding formula options with use of state-specific, county-level data. In order for this to run smoothly, please only input data into cells that are shaded </a:t>
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0"/>
+            <a:t>This workbook is designed to allow for easy calculation of funding formula </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0"/>
+            <a:t>options with use of state-specific, county-level data. In order for this to run </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0"/>
+            <a:t>smoothly, please only input data into cells that are shaded </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" u="none" baseline="0">
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="accent1">
                   <a:lumMod val="60000"/>
@@ -930,8 +887,20 @@
             </a:rPr>
             <a:t>BLUE. </a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" u="none" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" u="none" baseline="0">
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -940,7 +909,7 @@
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="2400" u="none" baseline="0">
+          <a:endParaRPr lang="en-US" sz="1600" u="none" baseline="0">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -948,7 +917,7 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" u="none" baseline="0">
+            <a:rPr lang="en-US" sz="1600" u="none" baseline="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -956,12 +925,36 @@
             <a:t>This funding formula template Excel sheet was </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="2400" baseline="0"/>
+            <a:rPr lang="en-US" sz="1600" baseline="0"/>
             <a:t>developed as part of a project funded by CDC's Office of Rural Health and the Federal Office of Rural Health Policy. Additional details about the project and additional deliverables as they become available can be found here: https://www.ruralhealthresearch.org/projects/1092. </a:t>
           </a:r>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="2400"/>
+          <a:endParaRPr lang="en-US" sz="1600" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" u="sng" baseline="0"/>
+            <a:t>Funding Statement:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t>This project was supported by the Health Resources and Services Administration (HRSA), U.S. Department of Health and Human Services (HHS) under the grant number U1CRH39978 Rural Health Research Grant Cooperative Agreement and the Centers for Disease Control and Prevention (CDC) Office of Rural Health. The information or content and conclusions are those of the authors and should not be construed as the official position or policy of, nor should any endorsements be inferred by HRSA, HHS, CDC, or the U.S. Government</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1600" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-US" sz="1600" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -970,15 +963,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>40821</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>122465</xdr:rowOff>
+      <xdr:colOff>142421</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>160565</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>176893</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>13608</xdr:rowOff>
+      <xdr:colOff>278493</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>51708</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -993,8 +986,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="40821" y="4653644"/>
-          <a:ext cx="3197679" cy="272143"/>
+          <a:off x="142421" y="5443765"/>
+          <a:ext cx="3628572" cy="272143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1030,8 +1023,8 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400"/>
-            <a:t>Example Data Structure</a:t>
+            <a:rPr lang="en-US" sz="1600"/>
+            <a:t>Example Data Structure:</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1041,15 +1034,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>54429</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>143328</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>102597</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>108858</xdr:rowOff>
+      <xdr:colOff>484713</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1065,15 +1058,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="54429" y="4912180"/>
-          <a:ext cx="7396025" cy="1251857"/>
+          <a:off x="143328" y="5816601"/>
+          <a:ext cx="8723385" cy="1371599"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1090,15 +1083,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>38098</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:colOff>126998</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>44449</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>310242</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>32656</xdr:rowOff>
+      <xdr:colOff>399142</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1114,7 +1107,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1128,8 +1121,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="38098" y="6452506"/>
-          <a:ext cx="8958944" cy="3344636"/>
+          <a:off x="126998" y="7613649"/>
+          <a:ext cx="10051144" cy="3613151"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1151,15 +1144,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>27215</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>136071</xdr:rowOff>
+      <xdr:colOff>154215</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>72571</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>163287</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>27214</xdr:rowOff>
+      <xdr:colOff>290287</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>154214</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1174,8 +1167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27215" y="6381750"/>
-          <a:ext cx="3197679" cy="272143"/>
+          <a:off x="154215" y="7260771"/>
+          <a:ext cx="3628572" cy="272143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1211,99 +1204,70 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1400"/>
+            <a:rPr lang="en-US" sz="1600"/>
             <a:t>Formula</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" baseline="0"/>
+            <a:rPr lang="en-US" sz="1600" baseline="0"/>
             <a:t> Names and Components</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400"/>
+          <a:endParaRPr lang="en-US" sz="1600"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>597277</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>47446</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>228755</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>12313</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>560716</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>115020</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>482601</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>16506</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AEB0139-2A06-4B6F-8165-8D8E8DB52357}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2625DA2A-1556-476C-8B63-3F8D760FEA8D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8634220" y="5237672"/>
-          <a:ext cx="9855062" cy="3431876"/>
+          <a:off x="7213755" y="202813"/>
+          <a:ext cx="1650846" cy="1096393"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
       </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400" u="sng" baseline="0"/>
-            <a:t>Funding Statement:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="2400">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t>This project was supported by the Health Resources and Services Administration (HRSA), U.S. Department of Health and Human Services (HHS) under the grant number U1CRH39978 Rural Health Research Grant Cooperative Agreement and the Centers for Disease Control and Prevention (CDC) Office of Rural Health. The information or content and conclusions are those of the authors and should not be construed as the official position or policy of, nor should any endorsements be inferred by HRSA, HHS, CDC, or the U.S. Government</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="2400" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="2400"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
